--- a/better-wealth-app/user_test_results.xlsx
+++ b/better-wealth-app/user_test_results.xlsx
@@ -7,8 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사용자테스트 결과" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="차수별 요약" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="페르소나 정의" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="사용자테스트 결과" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="차수별 요약" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -48,7 +49,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -80,6 +81,26 @@
         <fgColor rgb="FFF8F8F8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F2FD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF9C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3E5F5"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -107,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -153,6 +174,36 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -519,6 +570,375 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>페르소나</t>
+        </is>
+      </c>
+      <c r="B1" s="16" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="C1" s="16" t="inlineStr">
+        <is>
+          <t>나이</t>
+        </is>
+      </c>
+      <c r="D1" s="16" t="inlineStr">
+        <is>
+          <t>직업/직책</t>
+        </is>
+      </c>
+      <c r="E1" s="16" t="inlineStr">
+        <is>
+          <t>근속/경력</t>
+        </is>
+      </c>
+      <c r="F1" s="16" t="inlineStr">
+        <is>
+          <t>마이데이터 자산</t>
+        </is>
+      </c>
+      <c r="G1" s="16" t="inlineStr">
+        <is>
+          <t>DC 보유</t>
+        </is>
+      </c>
+      <c r="H1" s="16" t="inlineStr">
+        <is>
+          <t>국민연금</t>
+        </is>
+      </c>
+      <c r="I1" s="16" t="inlineStr">
+        <is>
+          <t>기타소득</t>
+        </is>
+      </c>
+      <c r="J1" s="16" t="inlineStr">
+        <is>
+          <t>특이사항</t>
+        </is>
+      </c>
+      <c r="K1" s="16" t="inlineStr">
+        <is>
+          <t>테스트 경로</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="52" customHeight="1">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>A 박은퇴</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="inlineStr">
+        <is>
+          <t>박은퇴</t>
+        </is>
+      </c>
+      <c r="C2" s="18" t="inlineStr">
+        <is>
+          <t>58세</t>
+        </is>
+      </c>
+      <c r="D2" s="18" t="inlineStr">
+        <is>
+          <t>대기업 부장</t>
+        </is>
+      </c>
+      <c r="E2" s="18" t="inlineStr">
+        <is>
+          <t>현 직장 근속 28년 / 이직 없음</t>
+        </is>
+      </c>
+      <c r="F2" s="18" t="inlineStr">
+        <is>
+          <t>있음 (IRP·DC·ISA)</t>
+        </is>
+      </c>
+      <c r="G2" s="18" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="H2" s="18" t="inlineStr">
+        <is>
+          <t>알고 있음 (직접입력)</t>
+        </is>
+      </c>
+      <c r="I2" s="18" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="J2" s="18" t="inlineStr">
+        <is>
+          <t>은퇴 2년 내 예정. 퇴직금 규모 큼. 안정적 단일 경력. 은퇴시기 60세로 변경 희망.</t>
+        </is>
+      </c>
+      <c r="K2" s="18" t="inlineStr">
+        <is>
+          <t>P1→P4→P5(안다)→P7→P8→P9(근로)→P10→P11(없음)→P13→P14→P15→P16</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="52" customHeight="1">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>B 이준비</t>
+        </is>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>이준비</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>45세</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>중소기업 과장</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>현 직장 근속 17년 (만 16년)</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>모름 (계산기 경로)</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>국민연금 계산기 경로 사용. P6 연소득 입력 후 P10 디폴트 자동 채움 검증 대상. 만 연수 개념 혼란 경험.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>P1→P4→P5(모른다)→P6→P9(근로)→P10→P11(없음)→P13→P14→P15→P16</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="52" customHeight="1">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>C 최자영</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="inlineStr">
+        <is>
+          <t>최자영</t>
+        </is>
+      </c>
+      <c r="C4" s="21" t="inlineStr">
+        <is>
+          <t>52세</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t>자영업자 (카페 운영)</t>
+        </is>
+      </c>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>자영업 12년 / 이전 직장 근로 8년</t>
+        </is>
+      </c>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t>있음 (IRP)</t>
+        </is>
+      </c>
+      <c r="G4" s="21" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H4" s="21" t="inlineStr">
+        <is>
+          <t>알고 있음 (직접입력)</t>
+        </is>
+      </c>
+      <c r="I4" s="21" t="inlineStr">
+        <is>
+          <t>임대소득 있음 (월세)</t>
+        </is>
+      </c>
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t>근로소득자 아님 → P10 미진입. P12 단일 임대소득 입력. P13 근로소득 행 미표시 검증 대상.</t>
+        </is>
+      </c>
+      <c r="K4" s="21" t="inlineStr">
+        <is>
+          <t>P1→P4→P5(안다)→P7→P9(비근로)→P11(있음)→P12→P13→P14→P15→P16</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="52" customHeight="1">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>D 정신입</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>정신입</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>34세</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>직장인 3년차 (스타트업)</t>
+        </is>
+      </c>
+      <c r="E5" s="23" t="inlineStr">
+        <is>
+          <t>현 직장 근속 3년</t>
+        </is>
+      </c>
+      <c r="F5" s="23" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="G5" s="23" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H5" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I5" s="23" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="J5" s="23" t="inlineStr">
+        <is>
+          <t>마이데이터 퇴직연금 자산 없음 → P3 자산없음 경고 후 이탈. 서비스 대상 외 케이스 검증 목적.</t>
+        </is>
+      </c>
+      <c r="K5" s="23" t="inlineStr">
+        <is>
+          <t>P1→P3(자산없음 경고)→이탈</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="24" t="inlineStr">
+        <is>
+          <t>E 한복잡</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>한복잡</t>
+        </is>
+      </c>
+      <c r="C6" s="25" t="inlineStr">
+        <is>
+          <t>55세</t>
+        </is>
+      </c>
+      <c r="D6" s="25" t="inlineStr">
+        <is>
+          <t>민간기업 차장 (前 공무원)</t>
+        </is>
+      </c>
+      <c r="E6" s="25" t="inlineStr">
+        <is>
+          <t>공무원 10년 + 현 직장 민간 8년 (이직)</t>
+        </is>
+      </c>
+      <c r="F6" s="25" t="inlineStr">
+        <is>
+          <t>있음 (IRP·DC)</t>
+        </is>
+      </c>
+      <c r="G6" s="25" t="inlineStr">
+        <is>
+          <t>있음 (DC)</t>
+        </is>
+      </c>
+      <c r="H6" s="25" t="inlineStr">
+        <is>
+          <t>모름 (계산기 경로)</t>
+        </is>
+      </c>
+      <c r="I6" s="25" t="inlineStr">
+        <is>
+          <t>임대소득 있음</t>
+        </is>
+      </c>
+      <c r="J6" s="25" t="inlineStr">
+        <is>
+          <t>이직 경력자 — 근속연수 기준 혼란 검증 대상. DC 보유 → P8 진입. 복잡한 자산 구조.</t>
+        </is>
+      </c>
+      <c r="K6" s="25" t="inlineStr">
+        <is>
+          <t>P1→P4→P5(모른다)→P6→P8→P9(근로)→P10→P11(있음)→P12→P13→P14→P15→P16</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1063,7 +1483,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
